--- a/ascend_test_suite/latest/SigInfer_model_list.xlsx
+++ b/ascend_test_suite/latest/SigInfer_model_list.xlsx
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm  --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7"  docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5  --model Meta-Llama-3.1-70B-Instruct --tokenizer /home/weight/Meta-Llama-3.1-70B-Instruct -tp 4 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008  --nnodes 1 --node-rank 0 --platform-type ascend  --swap-space 40 --tool-call-parser llama3_json</t>
+          <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm  --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7"  docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5  --model Meta-Llama-3.1-70B-Instruct --tokenizer /software/models/Meta-Llama-3.1-70B-Instruct -tp 8 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008  --nnodes 1 --node-rank 0 --platform-type ascend  --swap-space 40 --tool-call-parser llama3_json</t>
         </is>
       </c>
     </row>

--- a/ascend_test_suite/latest/SigInfer_model_list.xlsx
+++ b/ascend_test_suite/latest/SigInfer_model_list.xlsx
@@ -1200,8 +1200,7 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm  --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7"  docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5  --model DeepSeek-V3.1-Terminus-Channel-int8 --tokenizer /home/weight/DeepSeek-V3.1-Terminus-Channel-int8/ -tp 16 --port 8000 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --gpu-memory-utilization 0.97 --max-num-batched-tokens 2048 --master-addr 192.168.0.77 --master-port 8008 --nnodes 2 --node-rank 0 --swap-space 40 --tool-call-parser deepseek_v3  --tokens-per-prediction 1
-docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm  --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7"  docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5  --model DeepSeek-V3.1-Terminus-Channel-int8 --tokenizer /home/weight/DeepSeek-V3.1-Terminus-Channel-int8/ -tp 16 --port 8000 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --gpu-memory-utilization 0.97 --max-num-batched-tokens 2048 --master-addr 192.168.0.77 --master-port 8008 --nnodes 2 --node-rank 1 --swap-space 40 --tool-call-parser deepseek_v3  --tokens-per-prediction 1</t>
+          <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm  --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7"  docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5  --model DeepSeek-V3.1-Terminus-Channel-int8 --tokenizer /software/models/DeepSeek-V3.1-Terminus-Channel-int8/ -tp 8 --port 8000 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --gpu-memory-utilization 0.97 --max-num-batched-tokens 2048 --master-addr 192.168.0.77 --master-port 8008 --nnodes 1 --node-rank 0 --swap-space 40 --tool-call-parser deepseek_v3  --tokens-per-prediction 1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1308,7 +1307,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm  --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7"  docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5   --model DeepSeek-R1-Distill-Llama-70B --tokenizer /home/weight/DeepSeek-R1-Distill-Llama-70B -tp 4 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008  --nnodes 1 --node-rank 0 --platform-type ascend  --swap-space 40 --tool-call-parser llama3_json</t>
+          <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm  --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7"  docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5   --model DeepSeek-R1-Distill-Llama-70B --tokenizer /software/models/deepseek-ai/DeepSeek-R1-Distill-Llama-70B -tp 4 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008  --nnodes 1 --node-rank 0 --platform-type ascend  --swap-space 40 --tool-call-parser llama3_json</t>
         </is>
       </c>
     </row>
